--- a/WorkBook/Jutland ships.xlsx
+++ b/WorkBook/Jutland ships.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="196">
   <si>
     <t>年份</t>
   </si>
@@ -331,24 +331,48 @@
     <t>炮座侧舷</t>
   </si>
   <si>
+    <t>评级</t>
+  </si>
+  <si>
     <t>2.75s</t>
   </si>
   <si>
     <t>8m 11M</t>
   </si>
   <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>A:14</t>
+  </si>
+  <si>
     <t>1.75s</t>
   </si>
   <si>
     <t>9m 10M</t>
   </si>
   <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>B:12</t>
+  </si>
+  <si>
+    <t>C:11</t>
+  </si>
+  <si>
     <t>1.5+1.75</t>
   </si>
   <si>
+    <t>D:10.5</t>
+  </si>
+  <si>
     <t>7m 11M</t>
   </si>
   <si>
+    <t>E:9</t>
+  </si>
+  <si>
     <t>&amp;</t>
   </si>
   <si>
@@ -358,6 +382,12 @@
     <t>7m 10M</t>
   </si>
   <si>
+    <t>F:8</t>
+  </si>
+  <si>
+    <t>G:7</t>
+  </si>
+  <si>
     <t>1.75+1</t>
   </si>
   <si>
@@ -379,9 +409,15 @@
     <t>11m13</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>2s</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>4*</t>
   </si>
   <si>
@@ -424,12 +460,18 @@
     <t>30+30</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>30+40</t>
   </si>
   <si>
     <t>250m350</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>P</t>
   </si>
   <si>
@@ -440,6 +482,9 @@
   </si>
   <si>
     <t>180m230</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>35+50</t>
@@ -588,7 +633,7 @@
     <numFmt numFmtId="178" formatCode="0.0_ "/>
     <numFmt numFmtId="179" formatCode="0_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -627,6 +672,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -1138,128 +1191,128 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1327,6 +1380,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1734,7 +1790,7 @@
         <f>ROUND(AVERAGE(L2:M2),0)</f>
         <v>118</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="23">
         <v>120</v>
       </c>
     </row>
@@ -1780,7 +1836,7 @@
         <f t="shared" ref="O3:O30" si="3">ROUND(AVERAGE(L3:M3),0)</f>
         <v>124</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="23">
         <v>125</v>
       </c>
     </row>
@@ -1826,7 +1882,7 @@
         <f t="shared" si="3"/>
         <v>129</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="23">
         <v>130</v>
       </c>
     </row>
@@ -1872,7 +1928,7 @@
         <f t="shared" si="3"/>
         <v>130</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="23">
         <v>130</v>
       </c>
     </row>
@@ -1918,7 +1974,7 @@
         <f t="shared" si="3"/>
         <v>131</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="23">
         <v>130</v>
       </c>
     </row>
@@ -1964,7 +2020,7 @@
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="23">
         <v>145</v>
       </c>
     </row>
@@ -2010,7 +2066,7 @@
         <f t="shared" si="3"/>
         <v>159</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="23">
         <v>160</v>
       </c>
     </row>
@@ -2056,7 +2112,7 @@
         <f t="shared" si="3"/>
         <v>174</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="23">
         <v>175</v>
       </c>
     </row>
@@ -2102,7 +2158,7 @@
         <f t="shared" si="3"/>
         <v>146</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="23">
         <v>145</v>
       </c>
     </row>
@@ -2148,7 +2204,7 @@
         <f t="shared" si="3"/>
         <v>184</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="23">
         <v>185</v>
       </c>
     </row>
@@ -2194,7 +2250,7 @@
         <f t="shared" si="3"/>
         <v>178</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="23">
         <v>180</v>
       </c>
     </row>
@@ -2240,7 +2296,7 @@
         <f t="shared" si="3"/>
         <v>189</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="23">
         <v>190</v>
       </c>
     </row>
@@ -2286,7 +2342,7 @@
         <f t="shared" si="3"/>
         <v>199</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="23">
         <v>200</v>
       </c>
     </row>
@@ -2332,7 +2388,7 @@
         <f t="shared" si="3"/>
         <v>114</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="23">
         <v>115</v>
       </c>
     </row>
@@ -2378,7 +2434,7 @@
         <f t="shared" si="3"/>
         <v>125</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="23">
         <v>125</v>
       </c>
     </row>
@@ -2424,7 +2480,7 @@
         <f t="shared" si="3"/>
         <v>174</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="23">
         <v>170</v>
       </c>
     </row>
@@ -2470,11 +2526,11 @@
         <f t="shared" si="3"/>
         <v>187</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="23">
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="7:15">
+    <row r="19" spans="7:16">
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -2484,8 +2540,9 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="P19" s="23"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2498,6 +2555,7 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
+      <c r="P20" s="23"/>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="2">
@@ -2541,7 +2599,7 @@
         <f t="shared" si="3"/>
         <v>119</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="23">
         <v>120</v>
       </c>
     </row>
@@ -2587,7 +2645,7 @@
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="23">
         <v>145</v>
       </c>
     </row>
@@ -2633,7 +2691,7 @@
         <f t="shared" si="3"/>
         <v>156</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="23">
         <v>155</v>
       </c>
     </row>
@@ -2679,7 +2737,7 @@
         <f t="shared" si="3"/>
         <v>165</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="23">
         <v>165</v>
       </c>
     </row>
@@ -2725,7 +2783,7 @@
         <f t="shared" si="3"/>
         <v>184</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="23">
         <v>185</v>
       </c>
     </row>
@@ -2771,7 +2829,7 @@
         <f t="shared" si="3"/>
         <v>123</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="23">
         <v>125</v>
       </c>
     </row>
@@ -2817,7 +2875,7 @@
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="23">
         <v>150</v>
       </c>
     </row>
@@ -2863,7 +2921,7 @@
         <f t="shared" si="3"/>
         <v>162</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="23">
         <v>165</v>
       </c>
     </row>
@@ -2909,7 +2967,7 @@
         <f t="shared" si="3"/>
         <v>175</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="23">
         <v>175</v>
       </c>
     </row>
@@ -3082,7 +3140,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AR48"/>
   <sheetFormatPr defaultColWidth="9.00833333333333" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="5.375" style="1" customWidth="1"/>
@@ -3115,7 +3173,7 @@
     <col min="41" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39">
+    <row r="1" spans="1:42">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3224,8 +3282,11 @@
       <c r="AM1" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" spans="1:39">
+      <c r="AP1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44">
       <c r="A2" s="2">
         <v>1916</v>
       </c>
@@ -3274,7 +3335,7 @@
         <v>1.75</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Y2" s="5">
         <f>W2*0.5+0.5*2.75</f>
@@ -3322,13 +3383,19 @@
         <v>11</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AM2" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:39">
+      <c r="AP2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44">
       <c r="A3" s="2">
         <v>1916</v>
       </c>
@@ -3377,7 +3444,7 @@
         <v>1.75</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Y3" s="5">
         <f>W3*0.5+0.5*1.75</f>
@@ -3425,13 +3492,19 @@
         <v>11</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AM3" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:39">
+      <c r="AP3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44">
       <c r="A4" s="2">
         <v>1916</v>
       </c>
@@ -3480,7 +3553,7 @@
         <v>1.75</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Y4" s="5">
         <f>W4*0.5+0.5*1.75</f>
@@ -3528,13 +3601,19 @@
         <v>11</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AM4" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:39">
+      <c r="AP4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44">
       <c r="A5" s="2">
         <v>1916</v>
       </c>
@@ -3580,7 +3659,7 @@
       </c>
       <c r="V5" s="5"/>
       <c r="W5" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="X5" s="5"/>
       <c r="Y5" s="5">
@@ -3629,13 +3708,19 @@
         <v>11</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AM5" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:39">
+      <c r="AP5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44">
       <c r="A6" s="2">
         <v>1916</v>
       </c>
@@ -3681,7 +3766,7 @@
       </c>
       <c r="V6" s="5"/>
       <c r="W6" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="X6" s="5"/>
       <c r="Y6" s="5">
@@ -3730,13 +3815,19 @@
         <v>11</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="AM6" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:39">
+      <c r="AP6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44">
       <c r="A7" s="2">
         <v>1916</v>
       </c>
@@ -3759,7 +3850,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J7" s="6">
         <v>9</v>
@@ -3792,7 +3883,7 @@
       </c>
       <c r="V7" s="5"/>
       <c r="W7" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="X7" s="5"/>
       <c r="Y7" s="5">
@@ -3841,13 +3932,19 @@
         <v>11</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM7" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:39">
+      <c r="AP7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44">
       <c r="A8" s="2">
         <v>1916</v>
       </c>
@@ -3870,7 +3967,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J8" s="5">
         <v>9</v>
@@ -3905,7 +4002,7 @@
       </c>
       <c r="V8" s="5"/>
       <c r="W8" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="X8" s="5"/>
       <c r="Y8" s="5">
@@ -3954,13 +4051,19 @@
         <v>11</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM8" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:39">
+      <c r="AP8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:42">
       <c r="A9" s="2">
         <v>1916</v>
       </c>
@@ -3983,7 +4086,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J9" s="5">
         <v>9</v>
@@ -4018,7 +4121,7 @@
       </c>
       <c r="V9" s="5"/>
       <c r="W9" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="X9" s="5"/>
       <c r="Y9" s="5">
@@ -4067,13 +4170,16 @@
         <v>11</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM9" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:39">
+      <c r="AP9" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:42">
       <c r="A10" s="2">
         <v>1916</v>
       </c>
@@ -4096,7 +4202,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J10" s="5">
         <v>9</v>
@@ -4131,7 +4237,7 @@
       </c>
       <c r="V10" s="5"/>
       <c r="W10" s="5" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="X10" s="5"/>
       <c r="Y10" s="5">
@@ -4180,13 +4286,16 @@
         <v>11</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AM10" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:39">
+      <c r="AP10" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42">
       <c r="A11" s="2">
         <v>1916</v>
       </c>
@@ -4236,7 +4345,7 @@
       </c>
       <c r="V11" s="5"/>
       <c r="W11" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="X11" s="5"/>
       <c r="Y11" s="5">
@@ -4290,8 +4399,11 @@
       <c r="AM11" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:39">
+      <c r="AP11" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:42">
       <c r="A12" s="2">
         <v>1916</v>
       </c>
@@ -4310,14 +4422,14 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="J12" s="5">
         <v>9</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="M12" s="12">
         <f>9*0.7+6*0.3</f>
@@ -4345,7 +4457,7 @@
       </c>
       <c r="V12" s="5"/>
       <c r="W12" s="5" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="X12" s="5"/>
       <c r="Y12" s="5">
@@ -4391,7 +4503,7 @@
       </c>
       <c r="AJ12" s="5"/>
       <c r="AK12" s="5" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="AL12" s="5">
         <v>9</v>
@@ -4399,8 +4511,11 @@
       <c r="AM12" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:39">
+      <c r="AP12" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:42">
       <c r="A13" s="2">
         <v>1916</v>
       </c>
@@ -4449,7 +4564,7 @@
       </c>
       <c r="V13" s="5"/>
       <c r="W13" s="5" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="5">
@@ -4495,16 +4610,19 @@
       </c>
       <c r="AJ13" s="5"/>
       <c r="AK13" s="5" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM13" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:39">
+      <c r="AP13" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42">
       <c r="A14" s="2">
         <v>1916</v>
       </c>
@@ -4527,7 +4645,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J14" s="5">
         <v>9.5</v>
@@ -4536,7 +4654,7 @@
         <v>0.333333333333333</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M14" s="12">
         <f>G14*H14+J14*K14</f>
@@ -4564,7 +4682,7 @@
       </c>
       <c r="V14" s="5"/>
       <c r="W14" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="X14" s="5"/>
       <c r="Y14" s="5">
@@ -4610,16 +4728,19 @@
       </c>
       <c r="AJ14" s="5"/>
       <c r="AK14" s="5" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM14" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:39">
+      <c r="AP14" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:42">
       <c r="A15" s="2">
         <v>1916</v>
       </c>
@@ -4667,7 +4788,7 @@
         <v>1.5</v>
       </c>
       <c r="X15" s="5" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="Y15" s="5">
         <f>1.5*0.5+2*0.5</f>
@@ -4720,8 +4841,11 @@
       <c r="AM15" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:39">
+      <c r="AP15" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:42">
       <c r="A16" s="2">
         <v>1916</v>
       </c>
@@ -4740,14 +4864,14 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J16" s="5">
         <v>6</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="M16" s="12">
         <v>5</v>
@@ -4770,10 +4894,10 @@
       </c>
       <c r="V16" s="5"/>
       <c r="W16" s="5" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="X16" s="5" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="Y16" s="5">
         <f>(1.5/1+1)*0.5+2*0.5</f>
@@ -4826,12 +4950,15 @@
       <c r="AM16" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:39">
+      <c r="AP16" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:42">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F17" s="5">
         <v>6</v>
@@ -4839,14 +4966,14 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="J17" s="5">
         <v>6</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="M17" s="12">
         <v>5.5</v>
@@ -4869,10 +4996,10 @@
       </c>
       <c r="V17" s="5"/>
       <c r="W17" s="5" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="Y17" s="5">
         <f>(1.5/1+1)*0.5+2*0.5</f>
@@ -4916,11 +5043,20 @@
         <v>3.088125</v>
       </c>
       <c r="AJ17" s="5"/>
-      <c r="AK17" s="5"/>
-      <c r="AL17" s="5"/>
-      <c r="AM17" s="5"/>
-    </row>
-    <row r="18" spans="1:39">
+      <c r="AK17" s="5">
+        <v>7</v>
+      </c>
+      <c r="AL17" s="5">
+        <v>7</v>
+      </c>
+      <c r="AM17" s="5">
+        <v>7</v>
+      </c>
+      <c r="AP17" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:42">
       <c r="A18" s="2">
         <v>1916</v>
       </c>
@@ -4939,14 +5075,14 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J18" s="5">
         <v>9</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="M18" s="12">
         <f>9*0.7+5*0.3</f>
@@ -4959,7 +5095,7 @@
         <v>0.7</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="Q18" s="12">
         <f>(N18*0.7+5*0.3)*O18</f>
@@ -4976,7 +5112,7 @@
       </c>
       <c r="V18" s="5"/>
       <c r="W18" s="5" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="X18" s="5"/>
       <c r="Y18" s="5">
@@ -5025,13 +5161,16 @@
         <v>9</v>
       </c>
       <c r="AL18" s="5" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="AM18" s="5">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:39">
+      <c r="AP18" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:42">
       <c r="A19" s="2">
         <v>1916</v>
       </c>
@@ -5050,14 +5189,14 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="J19" s="5">
         <v>9</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="M19" s="12">
         <f>9*0.7+5*0.3</f>
@@ -5070,7 +5209,7 @@
         <v>0.7</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="Q19" s="12">
         <f>(N19*0.7+5*0.3)*O19</f>
@@ -5080,7 +5219,7 @@
         <v>6</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="13">
@@ -5089,7 +5228,7 @@
       </c>
       <c r="V19" s="5"/>
       <c r="W19" s="5" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="X19" s="5"/>
       <c r="Y19" s="5">
@@ -5142,6 +5281,9 @@
       </c>
       <c r="AM19" s="5">
         <v>9</v>
+      </c>
+      <c r="AP19" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="6:39">
@@ -5244,7 +5386,7 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:42">
       <c r="A22" s="2">
         <v>1916</v>
       </c>
@@ -5268,7 +5410,7 @@
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M22" s="12">
         <f>(F22*0.5+J22*0.5)/25.4</f>
@@ -5296,10 +5438,10 @@
       </c>
       <c r="V22" s="5"/>
       <c r="W22" s="5" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="X22" s="5" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="Y22" s="5">
         <f>(25+38)*0.5+58*0.5</f>
@@ -5356,8 +5498,11 @@
         <f>AM22/25.4</f>
         <v>11.0236220472441</v>
       </c>
-    </row>
-    <row r="23" spans="1:40">
+      <c r="AP22" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:42">
       <c r="A23" s="2">
         <v>1916</v>
       </c>
@@ -5407,10 +5552,10 @@
       </c>
       <c r="V23" s="5"/>
       <c r="W23" s="5" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="Y23" s="5">
         <f>(45+40)*0.5+60*0.5</f>
@@ -5455,20 +5600,23 @@
       </c>
       <c r="AJ23" s="5"/>
       <c r="AK23" s="5" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="AL23" s="5" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="AM23" s="5">
         <v>270</v>
       </c>
       <c r="AN23" s="22">
-        <f t="shared" ref="AN23:AN30" si="15">AM23/25.4</f>
+        <f>AM23/25.4</f>
         <v>10.6299212598425</v>
       </c>
-    </row>
-    <row r="24" spans="1:40">
+      <c r="AP23" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:42">
       <c r="A24" s="2">
         <v>1916</v>
       </c>
@@ -5491,7 +5639,7 @@
         <v>0.4</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J24" s="5">
         <v>350</v>
@@ -5501,7 +5649,7 @@
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="12">
-        <f t="shared" ref="M24:M29" si="16">(G24*H24+J24*K24)/25.4</f>
+        <f t="shared" ref="M24:M29" si="15">(G24*H24+J24*K24)/25.4</f>
         <v>12.4409448818898</v>
       </c>
       <c r="N24" s="5">
@@ -5528,7 +5676,7 @@
       </c>
       <c r="V24" s="5"/>
       <c r="W24" s="5" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="X24" s="5"/>
       <c r="Y24" s="5">
@@ -5574,7 +5722,7 @@
       </c>
       <c r="AJ24" s="5"/>
       <c r="AK24" s="5" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="AL24" s="5">
         <v>300</v>
@@ -5583,11 +5731,14 @@
         <v>300</v>
       </c>
       <c r="AN24" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="AN23:AN30" si="16">AM24/25.4</f>
         <v>11.8110236220472</v>
       </c>
-    </row>
-    <row r="25" spans="1:40">
+      <c r="AP24" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42">
       <c r="A25" s="2">
         <v>1916</v>
       </c>
@@ -5610,7 +5761,7 @@
         <v>0.4</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J25" s="5">
         <v>350</v>
@@ -5620,7 +5771,7 @@
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>12.4409448818898</v>
       </c>
       <c r="N25" s="5">
@@ -5647,7 +5798,7 @@
       </c>
       <c r="V25" s="5"/>
       <c r="W25" s="5" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="X25" s="5"/>
       <c r="Y25" s="5">
@@ -5693,7 +5844,7 @@
       </c>
       <c r="AJ25" s="5"/>
       <c r="AK25" s="5" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="AL25" s="5">
         <v>300</v>
@@ -5702,11 +5853,14 @@
         <v>300</v>
       </c>
       <c r="AN25" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>11.8110236220472</v>
       </c>
-    </row>
-    <row r="26" spans="1:40">
+      <c r="AP25" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:42">
       <c r="A26" s="2">
         <v>1916</v>
       </c>
@@ -5729,7 +5883,7 @@
         <v>0.4</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J26" s="5">
         <v>350</v>
@@ -5739,7 +5893,7 @@
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>12.3622047244094</v>
       </c>
       <c r="N26" s="5">
@@ -5766,7 +5920,7 @@
       </c>
       <c r="V26" s="5"/>
       <c r="W26" s="5" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="X26" s="5"/>
       <c r="Y26" s="5">
@@ -5812,7 +5966,7 @@
       </c>
       <c r="AJ26" s="5"/>
       <c r="AK26" s="5" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="AL26" s="5">
         <v>350</v>
@@ -5821,11 +5975,14 @@
         <v>350</v>
       </c>
       <c r="AN26" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13.7795275590551</v>
       </c>
-    </row>
-    <row r="27" spans="1:40">
+      <c r="AP26" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:42">
       <c r="A27" s="2">
         <v>1916</v>
       </c>
@@ -5848,7 +6005,7 @@
         <v>0.5</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J27" s="5">
         <v>200</v>
@@ -5857,10 +6014,10 @@
         <v>0.5</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>8.36614173228346</v>
       </c>
       <c r="N27" s="5">
@@ -5870,7 +6027,7 @@
         <v>0.2</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="Q27" s="12">
         <f>N27*O27*0.7/25.4</f>
@@ -5885,10 +6042,10 @@
       </c>
       <c r="V27" s="5"/>
       <c r="W27" s="5" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="X27" s="5" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="Y27" s="5">
         <f>(25+25)*0.5+50*0.5</f>
@@ -5933,7 +6090,7 @@
       </c>
       <c r="AJ27" s="5"/>
       <c r="AK27" s="5" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="AL27" s="5">
         <v>200</v>
@@ -5942,11 +6099,14 @@
         <v>200</v>
       </c>
       <c r="AN27" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.8740157480315</v>
       </c>
-    </row>
-    <row r="28" spans="1:40">
+      <c r="AP27" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:42">
       <c r="A28" s="2">
         <v>1916</v>
       </c>
@@ -5969,7 +6129,7 @@
         <v>0.5</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J28" s="5">
         <v>200</v>
@@ -5978,10 +6138,10 @@
         <v>0.5</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>8.56299212598425</v>
       </c>
       <c r="N28" s="5">
@@ -5991,7 +6151,7 @@
         <v>0.2</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="Q28" s="12">
         <f>N28*O28*0.7/25.4</f>
@@ -6008,7 +6168,7 @@
       </c>
       <c r="V28" s="5"/>
       <c r="W28" s="5" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="X28" s="5"/>
       <c r="Y28" s="5">
@@ -6054,7 +6214,7 @@
       </c>
       <c r="AJ28" s="5"/>
       <c r="AK28" s="5" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="AL28" s="5">
         <v>200</v>
@@ -6063,11 +6223,14 @@
         <v>200</v>
       </c>
       <c r="AN28" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.8740157480315</v>
       </c>
-    </row>
-    <row r="29" spans="1:40">
+      <c r="AP28" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:42">
       <c r="A29" s="2">
         <v>1916</v>
       </c>
@@ -6090,7 +6253,7 @@
         <v>0.5</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J29" s="5">
         <v>230</v>
@@ -6099,10 +6262,10 @@
         <v>0.5</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>9.64566929133858</v>
       </c>
       <c r="N29" s="5">
@@ -6112,7 +6275,7 @@
         <v>0.2</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="Q29" s="12">
         <f>N29*O29*0.7/25.4</f>
@@ -6129,7 +6292,7 @@
       </c>
       <c r="V29" s="5"/>
       <c r="W29" s="5" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="X29" s="5"/>
       <c r="Y29" s="5">
@@ -6175,7 +6338,7 @@
       </c>
       <c r="AJ29" s="5"/>
       <c r="AK29" s="5" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AL29" s="5">
         <v>230</v>
@@ -6184,11 +6347,14 @@
         <v>230</v>
       </c>
       <c r="AN29" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.05511811023622</v>
       </c>
-    </row>
-    <row r="30" spans="1:40">
+      <c r="AP29" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:42">
       <c r="A30" s="2">
         <v>1916</v>
       </c>
@@ -6240,7 +6406,7 @@
       </c>
       <c r="V30" s="5"/>
       <c r="W30" s="5" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="X30" s="5"/>
       <c r="Y30" s="5">
@@ -6286,7 +6452,7 @@
       </c>
       <c r="AJ30" s="5"/>
       <c r="AK30" s="5" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="AL30" s="5">
         <v>260</v>
@@ -6295,8 +6461,11 @@
         <v>260</v>
       </c>
       <c r="AN30" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>10.2362204724409</v>
+      </c>
+      <c r="AP30" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:39">
@@ -6335,19 +6504,19 @@
       <c r="X31" s="5"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="AA31" s="21" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="AB31" s="21" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="AC31" s="21" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="AD31" s="21" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="AE31" s="21"/>
       <c r="AF31" s="21"/>
@@ -6361,24 +6530,24 @@
     </row>
     <row r="32" spans="26:30">
       <c r="Z32" s="5" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="AA32" s="5" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="AB32" s="5" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="AC32" s="5" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="AD32" s="5" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:37">
       <c r="A33" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -6386,7 +6555,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -6418,7 +6587,7 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="8" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -6426,10 +6595,10 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -6446,7 +6615,7 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" s="8" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -6455,7 +6624,7 @@
       <c r="F35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -6483,7 +6652,7 @@
         <v>83</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -6515,7 +6684,7 @@
     </row>
     <row r="37" spans="1:37">
       <c r="A37" s="9" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -6526,7 +6695,7 @@
         <v>83</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -6558,7 +6727,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="9" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -6568,7 +6737,7 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="9" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -6576,7 +6745,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -6593,7 +6762,7 @@
     </row>
     <row r="40" spans="1:19">
       <c r="A40" s="9" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -6601,7 +6770,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="N40" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
@@ -6611,7 +6780,7 @@
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="8" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -6627,7 +6796,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -6637,7 +6806,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -6647,7 +6816,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -6657,7 +6826,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -6667,7 +6836,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -6677,7 +6846,7 @@
     </row>
     <row r="47" spans="1:38">
       <c r="A47" s="3" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -6685,7 +6854,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
@@ -6705,7 +6874,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -6801,7 +6970,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6818,7 +6987,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6835,7 +7004,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6852,7 +7021,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6869,7 +7038,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6886,7 +7055,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6903,7 +7072,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6920,7 +7089,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6937,7 +7106,7 @@
         <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6954,7 +7123,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6988,7 +7157,7 @@
         <v>37</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7005,7 +7174,7 @@
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7022,7 +7191,7 @@
         <v>44</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7039,7 +7208,7 @@
         <v>46</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7056,7 +7225,7 @@
         <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7073,7 +7242,7 @@
         <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="5:5">
@@ -7238,7 +7407,7 @@
     </row>
     <row r="31" spans="5:5">
       <c r="E31" s="3" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBook/Jutland ships.xlsx
+++ b/WorkBook/Jutland ships.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="198">
   <si>
     <t>年份</t>
   </si>
@@ -247,6 +247,12 @@
     <t>Deutschland</t>
   </si>
   <si>
+    <t>布伦瑞克</t>
+  </si>
+  <si>
+    <t>Braunschweig</t>
+  </si>
+  <si>
     <t>吨位/165.385</t>
   </si>
   <si>
@@ -409,40 +415,40 @@
     <t>11m13</t>
   </si>
   <si>
+    <t>2s</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>4*</t>
+  </si>
+  <si>
+    <t>1.5/1+1</t>
+  </si>
+  <si>
+    <t>澳、新西兰</t>
+  </si>
+  <si>
+    <t>5*</t>
+  </si>
+  <si>
+    <t>6-5*</t>
+  </si>
+  <si>
+    <t>1+1</t>
+  </si>
+  <si>
+    <t>8m9M</t>
+  </si>
+  <si>
+    <t>25+38</t>
+  </si>
+  <si>
+    <t>58s</t>
+  </si>
+  <si>
     <t>C</t>
-  </si>
-  <si>
-    <t>2s</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>4*</t>
-  </si>
-  <si>
-    <t>1.5/1+1</t>
-  </si>
-  <si>
-    <t>澳、新西兰</t>
-  </si>
-  <si>
-    <t>5*</t>
-  </si>
-  <si>
-    <t>6-5*</t>
-  </si>
-  <si>
-    <t>1+1</t>
-  </si>
-  <si>
-    <t>8m9M</t>
-  </si>
-  <si>
-    <t>25+38</t>
-  </si>
-  <si>
-    <t>58s</t>
   </si>
   <si>
     <t>45+40</t>
@@ -1312,7 +1318,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1365,6 +1371,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1696,7 +1705,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="5.375" style="1" customWidth="1"/>
@@ -1790,7 +1799,7 @@
         <f>ROUND(AVERAGE(L2:M2),0)</f>
         <v>118</v>
       </c>
-      <c r="P2" s="23">
+      <c r="P2" s="24">
         <v>120</v>
       </c>
     </row>
@@ -1836,7 +1845,7 @@
         <f t="shared" ref="O3:O30" si="3">ROUND(AVERAGE(L3:M3),0)</f>
         <v>124</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="24">
         <v>125</v>
       </c>
     </row>
@@ -1882,7 +1891,7 @@
         <f t="shared" si="3"/>
         <v>129</v>
       </c>
-      <c r="P4" s="23">
+      <c r="P4" s="24">
         <v>130</v>
       </c>
     </row>
@@ -1928,7 +1937,7 @@
         <f t="shared" si="3"/>
         <v>130</v>
       </c>
-      <c r="P5" s="23">
+      <c r="P5" s="24">
         <v>130</v>
       </c>
     </row>
@@ -1974,7 +1983,7 @@
         <f t="shared" si="3"/>
         <v>131</v>
       </c>
-      <c r="P6" s="23">
+      <c r="P6" s="24">
         <v>130</v>
       </c>
     </row>
@@ -2020,7 +2029,7 @@
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="P7" s="23">
+      <c r="P7" s="24">
         <v>145</v>
       </c>
     </row>
@@ -2066,7 +2075,7 @@
         <f t="shared" si="3"/>
         <v>159</v>
       </c>
-      <c r="P8" s="23">
+      <c r="P8" s="24">
         <v>160</v>
       </c>
     </row>
@@ -2112,7 +2121,7 @@
         <f t="shared" si="3"/>
         <v>174</v>
       </c>
-      <c r="P9" s="23">
+      <c r="P9" s="24">
         <v>175</v>
       </c>
     </row>
@@ -2158,7 +2167,7 @@
         <f t="shared" si="3"/>
         <v>146</v>
       </c>
-      <c r="P10" s="23">
+      <c r="P10" s="24">
         <v>145</v>
       </c>
     </row>
@@ -2204,7 +2213,7 @@
         <f t="shared" si="3"/>
         <v>184</v>
       </c>
-      <c r="P11" s="23">
+      <c r="P11" s="24">
         <v>185</v>
       </c>
     </row>
@@ -2250,7 +2259,7 @@
         <f t="shared" si="3"/>
         <v>178</v>
       </c>
-      <c r="P12" s="23">
+      <c r="P12" s="24">
         <v>180</v>
       </c>
     </row>
@@ -2296,7 +2305,7 @@
         <f t="shared" si="3"/>
         <v>189</v>
       </c>
-      <c r="P13" s="23">
+      <c r="P13" s="24">
         <v>190</v>
       </c>
     </row>
@@ -2342,7 +2351,7 @@
         <f t="shared" si="3"/>
         <v>199</v>
       </c>
-      <c r="P14" s="23">
+      <c r="P14" s="24">
         <v>200</v>
       </c>
     </row>
@@ -2388,7 +2397,7 @@
         <f t="shared" si="3"/>
         <v>114</v>
       </c>
-      <c r="P15" s="23">
+      <c r="P15" s="24">
         <v>115</v>
       </c>
     </row>
@@ -2434,7 +2443,7 @@
         <f t="shared" si="3"/>
         <v>125</v>
       </c>
-      <c r="P16" s="23">
+      <c r="P16" s="24">
         <v>125</v>
       </c>
     </row>
@@ -2480,7 +2489,7 @@
         <f t="shared" si="3"/>
         <v>174</v>
       </c>
-      <c r="P17" s="23">
+      <c r="P17" s="24">
         <v>170</v>
       </c>
     </row>
@@ -2526,7 +2535,7 @@
         <f t="shared" si="3"/>
         <v>187</v>
       </c>
-      <c r="P18" s="23">
+      <c r="P18" s="24">
         <v>185</v>
       </c>
     </row>
@@ -2540,7 +2549,7 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
-      <c r="P19" s="23"/>
+      <c r="P19" s="24"/>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="2"/>
@@ -2555,7 +2564,7 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
-      <c r="P20" s="23"/>
+      <c r="P20" s="24"/>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="2">
@@ -2599,7 +2608,7 @@
         <f t="shared" si="3"/>
         <v>119</v>
       </c>
-      <c r="P21" s="23">
+      <c r="P21" s="24">
         <v>120</v>
       </c>
     </row>
@@ -2645,7 +2654,7 @@
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="P22" s="23">
+      <c r="P22" s="24">
         <v>145</v>
       </c>
     </row>
@@ -2691,7 +2700,7 @@
         <f t="shared" si="3"/>
         <v>156</v>
       </c>
-      <c r="P23" s="23">
+      <c r="P23" s="24">
         <v>155</v>
       </c>
     </row>
@@ -2737,7 +2746,7 @@
         <f t="shared" si="3"/>
         <v>165</v>
       </c>
-      <c r="P24" s="23">
+      <c r="P24" s="24">
         <v>165</v>
       </c>
     </row>
@@ -2783,7 +2792,7 @@
         <f t="shared" si="3"/>
         <v>184</v>
       </c>
-      <c r="P25" s="23">
+      <c r="P25" s="24">
         <v>185</v>
       </c>
     </row>
@@ -2829,7 +2838,7 @@
         <f t="shared" si="3"/>
         <v>123</v>
       </c>
-      <c r="P26" s="23">
+      <c r="P26" s="24">
         <v>125</v>
       </c>
     </row>
@@ -2875,7 +2884,7 @@
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
-      <c r="P27" s="23">
+      <c r="P27" s="24">
         <v>150</v>
       </c>
     </row>
@@ -2921,7 +2930,7 @@
         <f t="shared" si="3"/>
         <v>162</v>
       </c>
-      <c r="P28" s="23">
+      <c r="P28" s="24">
         <v>165</v>
       </c>
     </row>
@@ -2967,11 +2976,11 @@
         <f t="shared" si="3"/>
         <v>175</v>
       </c>
-      <c r="P29" s="23">
+      <c r="P29" s="24">
         <v>175</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:16">
       <c r="A30" s="2">
         <v>1916</v>
       </c>
@@ -3013,24 +3022,56 @@
         <f t="shared" si="3"/>
         <v>83</v>
       </c>
-    </row>
-    <row r="31" spans="12:15">
-      <c r="L31" s="3" t="s">
+      <c r="P30" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="1">
+        <v>1916</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="3" t="s">
+      <c r="D31" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="G31" s="1">
+        <v>14394</v>
+      </c>
+      <c r="H31" s="1">
+        <v>13208</v>
+      </c>
+      <c r="I31" s="1">
+        <v>18</v>
+      </c>
+      <c r="J31" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="L31" s="5">
+        <f>ROUND(G31/165.385,0)</f>
+        <v>87</v>
+      </c>
+      <c r="M31" s="5">
+        <f>ROUND(H31/165.385,0)</f>
+        <v>80</v>
+      </c>
+      <c r="N31" s="5">
+        <f>L31-M31</f>
+        <v>7</v>
+      </c>
+      <c r="O31" s="5">
+        <f>ROUND(AVERAGE(L31:M31),0)</f>
+        <v>84</v>
+      </c>
+      <c r="P31" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="12:15">
       <c r="L32" s="3" t="s">
         <v>74</v>
       </c>
@@ -3038,7 +3079,7 @@
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:15">
       <c r="A33" s="3" t="s">
         <v>75</v>
       </c>
@@ -3047,10 +3088,16 @@
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
+      <c r="L33" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -3058,23 +3105,19 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
+    <row r="35" spans="1:6">
+      <c r="A35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="9" t="s">
-        <v>78</v>
+      <c r="A37" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -3087,8 +3130,8 @@
       <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="8" t="s">
-        <v>79</v>
+      <c r="A38" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -3101,8 +3144,8 @@
       <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="8" t="s">
-        <v>80</v>
+      <c r="A39" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -3114,22 +3157,36 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
     </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="L32:O32"/>
     <mergeCell ref="A33:F33"/>
+    <mergeCell ref="L33:O33"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A37:J37"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A40:J40"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A37" r:id="rId1" display="https://www.bilibili.com/read/cv34684600"/>
-    <hyperlink ref="A38" r:id="rId2" display="https://tieba.baidu.com/p/10710367839" tooltip="https://tieba.baidu.com/p/10710367839"/>
-    <hyperlink ref="A39" r:id="rId3" display="https://www.warship1.cn/forum.php?mod=viewthread&amp;tid=7352"/>
+    <hyperlink ref="A38" r:id="rId1" display="https://www.bilibili.com/read/cv34684600"/>
+    <hyperlink ref="A39" r:id="rId2" display="https://tieba.baidu.com/p/10710367839" tooltip="https://tieba.baidu.com/p/10710367839"/>
+    <hyperlink ref="A40" r:id="rId3" display="https://www.warship1.cn/forum.php?mod=viewthread&amp;tid=7352"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3187,103 +3244,103 @@
         <v>3</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N1" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="Q1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="T1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="U1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="U1" s="11" t="s">
-        <v>86</v>
-      </c>
       <c r="V1" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="W1" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Y1" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Z1" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AB1" s="16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AC1" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD1" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF1" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AD1" s="15" t="s">
+      <c r="AG1" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="AF1" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG1" s="16" t="s">
-        <v>94</v>
-      </c>
       <c r="AH1" s="16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AI1" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:44">
@@ -3335,7 +3392,7 @@
         <v>1.75</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y2" s="5">
         <f>W2*0.5+0.5*2.75</f>
@@ -3383,16 +3440,16 @@
         <v>11</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AM2" s="5">
         <v>10</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -3444,7 +3501,7 @@
         <v>1.75</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Y3" s="5">
         <f>W3*0.5+0.5*1.75</f>
@@ -3492,16 +3549,16 @@
         <v>11</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM3" s="5">
         <v>9</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -3553,7 +3610,7 @@
         <v>1.75</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Y4" s="5">
         <f>W4*0.5+0.5*1.75</f>
@@ -3601,16 +3658,16 @@
         <v>11</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM4" s="5">
         <v>9</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AR4" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:44">
@@ -3659,7 +3716,7 @@
       </c>
       <c r="V5" s="5"/>
       <c r="W5" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="X5" s="5"/>
       <c r="Y5" s="5">
@@ -3708,16 +3765,16 @@
         <v>11</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM5" s="5">
         <v>9</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AR5" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:44">
@@ -3766,7 +3823,7 @@
       </c>
       <c r="V6" s="5"/>
       <c r="W6" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="X6" s="5"/>
       <c r="Y6" s="5">
@@ -3815,16 +3872,16 @@
         <v>11</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AM6" s="5">
         <v>10</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AR6" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:44">
@@ -3850,7 +3907,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J7" s="6">
         <v>9</v>
@@ -3883,7 +3940,7 @@
       </c>
       <c r="V7" s="5"/>
       <c r="W7" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="X7" s="5"/>
       <c r="Y7" s="5">
@@ -3894,19 +3951,19 @@
         <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
-      <c r="AA7" s="17">
+      <c r="AA7" s="18">
         <f t="shared" si="5"/>
         <v>13.6</v>
       </c>
-      <c r="AB7" s="17">
+      <c r="AB7" s="18">
         <f t="shared" si="6"/>
         <v>14.85</v>
       </c>
-      <c r="AC7" s="17">
+      <c r="AC7" s="18">
         <f t="shared" si="7"/>
         <v>12.656</v>
       </c>
-      <c r="AD7" s="17">
+      <c r="AD7" s="18">
         <f t="shared" si="8"/>
         <v>11.6025</v>
       </c>
@@ -3932,16 +3989,16 @@
         <v>11</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AM7" s="5">
         <v>10</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AR7" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:44">
@@ -3967,7 +4024,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J8" s="5">
         <v>9</v>
@@ -4002,7 +4059,7 @@
       </c>
       <c r="V8" s="5"/>
       <c r="W8" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="X8" s="5"/>
       <c r="Y8" s="5">
@@ -4013,19 +4070,19 @@
         <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
-      <c r="AA8" s="17">
+      <c r="AA8" s="18">
         <f t="shared" si="5"/>
         <v>13.6</v>
       </c>
-      <c r="AB8" s="17">
+      <c r="AB8" s="18">
         <f t="shared" si="6"/>
         <v>14.85</v>
       </c>
-      <c r="AC8" s="17">
+      <c r="AC8" s="18">
         <f t="shared" si="7"/>
         <v>12.656</v>
       </c>
-      <c r="AD8" s="17">
+      <c r="AD8" s="18">
         <f t="shared" si="8"/>
         <v>11.6025</v>
       </c>
@@ -4051,16 +4108,16 @@
         <v>11</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AM8" s="5">
         <v>10</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AR8" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:42">
@@ -4086,7 +4143,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J9" s="5">
         <v>9</v>
@@ -4121,7 +4178,7 @@
       </c>
       <c r="V9" s="5"/>
       <c r="W9" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="X9" s="5"/>
       <c r="Y9" s="5">
@@ -4132,19 +4189,19 @@
         <f t="shared" si="4"/>
         <v>2.75</v>
       </c>
-      <c r="AA9" s="17">
+      <c r="AA9" s="18">
         <f t="shared" si="5"/>
         <v>13.975</v>
       </c>
-      <c r="AB9" s="17">
+      <c r="AB9" s="18">
         <f t="shared" si="6"/>
         <v>15.35</v>
       </c>
-      <c r="AC9" s="17">
+      <c r="AC9" s="18">
         <f t="shared" si="7"/>
         <v>12.976</v>
       </c>
-      <c r="AD9" s="17">
+      <c r="AD9" s="18">
         <f t="shared" si="8"/>
         <v>11.87625</v>
       </c>
@@ -4170,13 +4227,13 @@
         <v>11</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AM9" s="5">
         <v>10</v>
       </c>
       <c r="AP9" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:42">
@@ -4202,7 +4259,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J10" s="5">
         <v>9</v>
@@ -4237,7 +4294,7 @@
       </c>
       <c r="V10" s="5"/>
       <c r="W10" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X10" s="5"/>
       <c r="Y10" s="5">
@@ -4248,19 +4305,19 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="AA10" s="17">
+      <c r="AA10" s="18">
         <f t="shared" si="5"/>
         <v>14.35</v>
       </c>
-      <c r="AB10" s="17">
+      <c r="AB10" s="18">
         <f t="shared" si="6"/>
         <v>15.85</v>
       </c>
-      <c r="AC10" s="17">
+      <c r="AC10" s="18">
         <f t="shared" si="7"/>
         <v>13.296</v>
       </c>
-      <c r="AD10" s="17">
+      <c r="AD10" s="18">
         <f t="shared" si="8"/>
         <v>12.15</v>
       </c>
@@ -4286,13 +4343,13 @@
         <v>11</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM10" s="5">
         <v>9</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:42">
@@ -4345,7 +4402,7 @@
       </c>
       <c r="V11" s="5"/>
       <c r="W11" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="X11" s="5"/>
       <c r="Y11" s="5">
@@ -4400,7 +4457,7 @@
         <v>10</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:42">
@@ -4422,14 +4479,14 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J12" s="5">
         <v>9</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M12" s="12">
         <f>9*0.7+6*0.3</f>
@@ -4457,7 +4514,7 @@
       </c>
       <c r="V12" s="5"/>
       <c r="W12" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="X12" s="5"/>
       <c r="Y12" s="5">
@@ -4503,7 +4560,7 @@
       </c>
       <c r="AJ12" s="5"/>
       <c r="AK12" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AL12" s="5">
         <v>9</v>
@@ -4512,7 +4569,7 @@
         <v>9</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:42">
@@ -4564,7 +4621,7 @@
       </c>
       <c r="V13" s="5"/>
       <c r="W13" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="5">
@@ -4610,16 +4667,16 @@
       </c>
       <c r="AJ13" s="5"/>
       <c r="AK13" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AM13" s="5">
         <v>10</v>
       </c>
       <c r="AP13" s="1" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:42">
@@ -4645,7 +4702,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J14" s="5">
         <v>9.5</v>
@@ -4654,7 +4711,7 @@
         <v>0.333333333333333</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M14" s="12">
         <f>G14*H14+J14*K14</f>
@@ -4682,7 +4739,7 @@
       </c>
       <c r="V14" s="5"/>
       <c r="W14" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="X14" s="5"/>
       <c r="Y14" s="5">
@@ -4697,7 +4754,7 @@
         <f t="shared" si="5"/>
         <v>14.015</v>
       </c>
-      <c r="AB14" s="17">
+      <c r="AB14" s="18">
         <f t="shared" si="6"/>
         <v>15.265</v>
       </c>
@@ -4728,16 +4785,16 @@
       </c>
       <c r="AJ14" s="5"/>
       <c r="AK14" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AM14" s="5">
         <v>10</v>
       </c>
       <c r="AP14" s="1" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:42">
@@ -4788,7 +4845,7 @@
         <v>1.5</v>
       </c>
       <c r="X15" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y15" s="5">
         <f>1.5*0.5+2*0.5</f>
@@ -4842,7 +4899,7 @@
         <v>7</v>
       </c>
       <c r="AP15" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:42">
@@ -4864,14 +4921,14 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J16" s="5">
         <v>6</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M16" s="12">
         <v>5</v>
@@ -4894,10 +4951,10 @@
       </c>
       <c r="V16" s="5"/>
       <c r="W16" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="X16" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y16" s="5">
         <f>(1.5/1+1)*0.5+2*0.5</f>
@@ -4951,14 +5008,14 @@
         <v>7</v>
       </c>
       <c r="AP16" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:42">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F17" s="5">
         <v>6</v>
@@ -4966,14 +5023,14 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J17" s="5">
         <v>6</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" s="12">
         <v>5.5</v>
@@ -4996,10 +5053,10 @@
       </c>
       <c r="V17" s="5"/>
       <c r="W17" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y17" s="5">
         <f>(1.5/1+1)*0.5+2*0.5</f>
@@ -5053,7 +5110,7 @@
         <v>7</v>
       </c>
       <c r="AP17" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:42">
@@ -5075,14 +5132,14 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J18" s="5">
         <v>9</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M18" s="12">
         <f>9*0.7+5*0.3</f>
@@ -5095,7 +5152,7 @@
         <v>0.7</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q18" s="12">
         <f>(N18*0.7+5*0.3)*O18</f>
@@ -5112,7 +5169,7 @@
       </c>
       <c r="V18" s="5"/>
       <c r="W18" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X18" s="5"/>
       <c r="Y18" s="5">
@@ -5161,13 +5218,13 @@
         <v>9</v>
       </c>
       <c r="AL18" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AM18" s="5">
         <v>8.5</v>
       </c>
       <c r="AP18" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:42">
@@ -5189,14 +5246,14 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J19" s="5">
         <v>9</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M19" s="12">
         <f>9*0.7+5*0.3</f>
@@ -5209,7 +5266,7 @@
         <v>0.7</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q19" s="12">
         <f>(N19*0.7+5*0.3)*O19</f>
@@ -5219,7 +5276,7 @@
         <v>6</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="13">
@@ -5228,7 +5285,7 @@
       </c>
       <c r="V19" s="5"/>
       <c r="W19" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X19" s="5"/>
       <c r="Y19" s="5">
@@ -5239,19 +5296,19 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AA19" s="18">
+      <c r="AA19" s="19">
         <f t="shared" si="5"/>
         <v>10.94475</v>
       </c>
-      <c r="AB19" s="18">
+      <c r="AB19" s="19">
         <f t="shared" si="6"/>
         <v>11.94475</v>
       </c>
-      <c r="AC19" s="18">
+      <c r="AC19" s="19">
         <f t="shared" si="7"/>
         <v>10.18696</v>
       </c>
-      <c r="AD19" s="18">
+      <c r="AD19" s="19">
         <f t="shared" si="8"/>
         <v>9.340275</v>
       </c>
@@ -5283,7 +5340,7 @@
         <v>9</v>
       </c>
       <c r="AP19" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="6:39">
@@ -5308,10 +5365,10 @@
       <c r="X20" s="5"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="13"/>
-      <c r="AA20" s="19"/>
-      <c r="AB20" s="19"/>
-      <c r="AC20" s="19"/>
-      <c r="AD20" s="19"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="20"/>
       <c r="AE20" s="5"/>
       <c r="AF20" s="17">
         <f t="shared" si="9"/>
@@ -5360,10 +5417,10 @@
       <c r="X21" s="5"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="13"/>
-      <c r="AA21" s="19"/>
-      <c r="AB21" s="19"/>
-      <c r="AC21" s="19"/>
-      <c r="AD21" s="19"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
       <c r="AE21" s="5"/>
       <c r="AF21" s="17">
         <f t="shared" si="9"/>
@@ -5410,7 +5467,7 @@
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M22" s="12">
         <f>(F22*0.5+J22*0.5)/25.4</f>
@@ -5438,10 +5495,10 @@
       </c>
       <c r="V22" s="5"/>
       <c r="W22" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="X22" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Y22" s="5">
         <f>(25+38)*0.5+58*0.5</f>
@@ -5451,19 +5508,19 @@
         <f>(Y22+T22)/25.4</f>
         <v>2.38188976377953</v>
       </c>
-      <c r="AA22" s="20">
+      <c r="AA22" s="21">
         <f t="shared" si="5"/>
         <v>12.2746062992126</v>
       </c>
-      <c r="AB22" s="20">
+      <c r="AB22" s="21">
         <f t="shared" si="6"/>
         <v>13.4655511811024</v>
       </c>
-      <c r="AC22" s="20">
+      <c r="AC22" s="21">
         <f t="shared" si="7"/>
         <v>11.4025196850394</v>
       </c>
-      <c r="AD22" s="20">
+      <c r="AD22" s="21">
         <f t="shared" si="8"/>
         <v>10.4397637795276</v>
       </c>
@@ -5494,12 +5551,12 @@
       <c r="AM22" s="5">
         <v>280</v>
       </c>
-      <c r="AN22" s="22">
+      <c r="AN22" s="23">
         <f>AM22/25.4</f>
         <v>11.0236220472441</v>
       </c>
       <c r="AP22" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:42">
@@ -5552,10 +5609,10 @@
       </c>
       <c r="V23" s="5"/>
       <c r="W23" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Y23" s="5">
         <f>(45+40)*0.5+60*0.5</f>
@@ -5600,20 +5657,20 @@
       </c>
       <c r="AJ23" s="5"/>
       <c r="AK23" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AL23" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AM23" s="5">
         <v>270</v>
       </c>
-      <c r="AN23" s="22">
+      <c r="AN23" s="23">
         <f>AM23/25.4</f>
         <v>10.6299212598425</v>
       </c>
       <c r="AP23" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:42">
@@ -5639,7 +5696,7 @@
         <v>0.4</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J24" s="5">
         <v>350</v>
@@ -5676,7 +5733,7 @@
       </c>
       <c r="V24" s="5"/>
       <c r="W24" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="X24" s="5"/>
       <c r="Y24" s="5">
@@ -5722,7 +5779,7 @@
       </c>
       <c r="AJ24" s="5"/>
       <c r="AK24" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AL24" s="5">
         <v>300</v>
@@ -5730,12 +5787,12 @@
       <c r="AM24" s="5">
         <v>300</v>
       </c>
-      <c r="AN24" s="22">
+      <c r="AN24" s="23">
         <f t="shared" ref="AN23:AN30" si="16">AM24/25.4</f>
         <v>11.8110236220472</v>
       </c>
       <c r="AP24" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:42">
@@ -5761,7 +5818,7 @@
         <v>0.4</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J25" s="5">
         <v>350</v>
@@ -5798,7 +5855,7 @@
       </c>
       <c r="V25" s="5"/>
       <c r="W25" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="X25" s="5"/>
       <c r="Y25" s="5">
@@ -5844,7 +5901,7 @@
       </c>
       <c r="AJ25" s="5"/>
       <c r="AK25" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AL25" s="5">
         <v>300</v>
@@ -5852,12 +5909,12 @@
       <c r="AM25" s="5">
         <v>300</v>
       </c>
-      <c r="AN25" s="22">
+      <c r="AN25" s="23">
         <f t="shared" si="16"/>
         <v>11.8110236220472</v>
       </c>
       <c r="AP25" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:42">
@@ -5883,7 +5940,7 @@
         <v>0.4</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J26" s="5">
         <v>350</v>
@@ -5920,7 +5977,7 @@
       </c>
       <c r="V26" s="5"/>
       <c r="W26" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="X26" s="5"/>
       <c r="Y26" s="5">
@@ -5966,7 +6023,7 @@
       </c>
       <c r="AJ26" s="5"/>
       <c r="AK26" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AL26" s="5">
         <v>350</v>
@@ -5974,12 +6031,12 @@
       <c r="AM26" s="5">
         <v>350</v>
       </c>
-      <c r="AN26" s="22">
+      <c r="AN26" s="23">
         <f t="shared" si="16"/>
         <v>13.7795275590551</v>
       </c>
       <c r="AP26" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:42">
@@ -6005,7 +6062,7 @@
         <v>0.5</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J27" s="5">
         <v>200</v>
@@ -6014,7 +6071,7 @@
         <v>0.5</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M27" s="12">
         <f t="shared" si="15"/>
@@ -6027,7 +6084,7 @@
         <v>0.2</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q27" s="12">
         <f>N27*O27*0.7/25.4</f>
@@ -6042,10 +6099,10 @@
       </c>
       <c r="V27" s="5"/>
       <c r="W27" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="X27" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Y27" s="5">
         <f>(25+25)*0.5+50*0.5</f>
@@ -6090,7 +6147,7 @@
       </c>
       <c r="AJ27" s="5"/>
       <c r="AK27" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL27" s="5">
         <v>200</v>
@@ -6098,12 +6155,12 @@
       <c r="AM27" s="5">
         <v>200</v>
       </c>
-      <c r="AN27" s="22">
+      <c r="AN27" s="23">
         <f t="shared" si="16"/>
         <v>7.8740157480315</v>
       </c>
       <c r="AP27" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:42">
@@ -6129,7 +6186,7 @@
         <v>0.5</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J28" s="5">
         <v>200</v>
@@ -6138,7 +6195,7 @@
         <v>0.5</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M28" s="12">
         <f t="shared" si="15"/>
@@ -6151,7 +6208,7 @@
         <v>0.2</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q28" s="12">
         <f>N28*O28*0.7/25.4</f>
@@ -6168,7 +6225,7 @@
       </c>
       <c r="V28" s="5"/>
       <c r="W28" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="X28" s="5"/>
       <c r="Y28" s="5">
@@ -6214,7 +6271,7 @@
       </c>
       <c r="AJ28" s="5"/>
       <c r="AK28" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL28" s="5">
         <v>200</v>
@@ -6222,12 +6279,12 @@
       <c r="AM28" s="5">
         <v>200</v>
       </c>
-      <c r="AN28" s="22">
+      <c r="AN28" s="23">
         <f t="shared" si="16"/>
         <v>7.8740157480315</v>
       </c>
       <c r="AP28" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:42">
@@ -6253,7 +6310,7 @@
         <v>0.5</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J29" s="5">
         <v>230</v>
@@ -6262,7 +6319,7 @@
         <v>0.5</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M29" s="12">
         <f t="shared" si="15"/>
@@ -6275,7 +6332,7 @@
         <v>0.2</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q29" s="12">
         <f>N29*O29*0.7/25.4</f>
@@ -6292,7 +6349,7 @@
       </c>
       <c r="V29" s="5"/>
       <c r="W29" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="X29" s="5"/>
       <c r="Y29" s="5">
@@ -6338,7 +6395,7 @@
       </c>
       <c r="AJ29" s="5"/>
       <c r="AK29" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AL29" s="5">
         <v>230</v>
@@ -6346,12 +6403,12 @@
       <c r="AM29" s="5">
         <v>230</v>
       </c>
-      <c r="AN29" s="22">
+      <c r="AN29" s="23">
         <f t="shared" si="16"/>
         <v>9.05511811023622</v>
       </c>
       <c r="AP29" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:42">
@@ -6406,7 +6463,7 @@
       </c>
       <c r="V30" s="5"/>
       <c r="W30" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="X30" s="5"/>
       <c r="Y30" s="5">
@@ -6452,7 +6509,7 @@
       </c>
       <c r="AJ30" s="5"/>
       <c r="AK30" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AL30" s="5">
         <v>260</v>
@@ -6460,12 +6517,12 @@
       <c r="AM30" s="5">
         <v>260</v>
       </c>
-      <c r="AN30" s="22">
+      <c r="AN30" s="23">
         <f t="shared" si="16"/>
         <v>10.2362204724409</v>
       </c>
       <c r="AP30" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:39">
@@ -6504,50 +6561,50 @@
       <c r="X31" s="5"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA31" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB31" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="AC31" s="21" t="s">
+      <c r="AA31" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="AD31" s="21" t="s">
+      <c r="AB31" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="AE31" s="21"/>
-      <c r="AF31" s="21"/>
-      <c r="AG31" s="21"/>
-      <c r="AH31" s="21"/>
-      <c r="AI31" s="21"/>
-      <c r="AJ31" s="21"/>
+      <c r="AC31" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD31" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE31" s="22"/>
+      <c r="AF31" s="22"/>
+      <c r="AG31" s="22"/>
+      <c r="AH31" s="22"/>
+      <c r="AI31" s="22"/>
+      <c r="AJ31" s="22"/>
       <c r="AK31" s="5"/>
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
     <row r="32" spans="26:30">
       <c r="Z32" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AA32" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AB32" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AC32" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AD32" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:37">
       <c r="A33" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -6555,7 +6612,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -6587,7 +6644,7 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -6595,10 +6652,10 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -6615,7 +6672,7 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -6624,7 +6681,7 @@
       <c r="F35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -6641,7 +6698,7 @@
     </row>
     <row r="36" spans="1:37">
       <c r="A36" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -6649,10 +6706,10 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="I36" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -6684,7 +6741,7 @@
     </row>
     <row r="37" spans="1:37">
       <c r="A37" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -6692,10 +6749,10 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="I37" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -6727,7 +6784,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -6737,7 +6794,7 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -6745,7 +6802,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -6762,7 +6819,7 @@
     </row>
     <row r="40" spans="1:19">
       <c r="A40" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -6770,7 +6827,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="N40" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
@@ -6780,7 +6837,7 @@
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -6796,7 +6853,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -6806,7 +6863,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -6816,7 +6873,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -6826,7 +6883,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -6836,7 +6893,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -6846,7 +6903,7 @@
     </row>
     <row r="47" spans="1:38">
       <c r="A47" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -6854,7 +6911,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
@@ -6874,7 +6931,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -6970,7 +7027,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6987,7 +7044,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7004,7 +7061,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7021,7 +7078,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7038,7 +7095,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7055,7 +7112,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7072,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7089,7 +7146,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7106,7 +7163,7 @@
         <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7123,7 +7180,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7157,7 +7214,7 @@
         <v>37</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7174,7 +7231,7 @@
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7191,7 +7248,7 @@
         <v>44</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7208,7 +7265,7 @@
         <v>46</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7225,7 +7282,7 @@
         <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7242,7 +7299,7 @@
         <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="5:5">
@@ -7407,7 +7464,7 @@
     </row>
     <row r="31" spans="5:5">
       <c r="E31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBook/Jutland ships.xlsx
+++ b/WorkBook/Jutland ships.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="200">
   <si>
     <t>年份</t>
   </si>
@@ -505,6 +505,18 @@
     <t>220m270</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>John Robert《Battlecrusier》</t>
+  </si>
+  <si>
+    <t>单位：in,mm</t>
+  </si>
+  <si>
     <t>%</t>
   </si>
   <si>
@@ -520,6 +532,15 @@
     <t>0.27</t>
   </si>
   <si>
+    <t>https://www.warship1.cn/thread-7433-1-1.html</t>
+  </si>
+  <si>
+    <t>R=1</t>
+  </si>
+  <si>
+    <t>SideM：水线最厚 LowerDeck to MiddleDeck</t>
+  </si>
+  <si>
     <t>*</t>
   </si>
   <si>
@@ -533,21 +554,6 @@
   </si>
   <si>
     <t>2.5,2</t>
-  </si>
-  <si>
-    <t>John Robert《Battlecrusier》</t>
-  </si>
-  <si>
-    <t>单位：in,mm</t>
-  </si>
-  <si>
-    <t>https://www.warship1.cn/thread-7433-1-1.html</t>
-  </si>
-  <si>
-    <t>R=1</t>
-  </si>
-  <si>
-    <t>SideM：水线最厚 LowerDeck to MiddleDeck</t>
   </si>
   <si>
     <t>https://www.warship1.cn/thread-7435-1-1.html</t>
@@ -1705,7 +1711,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="5.375" style="1" customWidth="1"/>
@@ -1830,19 +1836,19 @@
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5">
-        <f t="shared" ref="L3:L30" si="0">ROUND(G3/165.385,0)</f>
+        <f t="shared" ref="L3:L36" si="0">ROUND(G3/165.385,0)</f>
         <v>136</v>
       </c>
       <c r="M3" s="5">
-        <f t="shared" ref="M3:M30" si="1">ROUND(H3/165.385,0)</f>
+        <f t="shared" ref="M3:M31" si="1">ROUND(H3/165.385,0)</f>
         <v>112</v>
       </c>
       <c r="N3" s="5">
-        <f t="shared" ref="N3:N30" si="2">L3-M3</f>
+        <f t="shared" ref="N3:N31" si="2">L3-M3</f>
         <v>24</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" ref="O3:O30" si="3">ROUND(AVERAGE(L3:M3),0)</f>
+        <f t="shared" ref="O3:O31" si="3">ROUND(AVERAGE(L3:M3),0)</f>
         <v>124</v>
       </c>
       <c r="P3" s="24">
@@ -3052,141 +3058,195 @@
         <v>18.5</v>
       </c>
       <c r="L31" s="5">
-        <f>ROUND(G31/165.385,0)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="M31" s="5">
-        <f>ROUND(H31/165.385,0)</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="N31" s="5">
-        <f>L31-M31</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O31" s="5">
-        <f>ROUND(AVERAGE(L31:M31),0)</f>
+        <f t="shared" si="3"/>
         <v>84</v>
       </c>
       <c r="P31" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="12:15">
-      <c r="L32" s="3" t="s">
+    <row r="32" spans="7:16">
+      <c r="G32" s="1">
+        <v>11000</v>
+      </c>
+      <c r="L32" s="5">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="P32" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="7:16">
+      <c r="G33" s="1">
+        <v>559</v>
+      </c>
+      <c r="L33" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P33" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="7:16">
+      <c r="G34" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L34" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="P34" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="7:12">
+      <c r="G35" s="1">
+        <v>3440</v>
+      </c>
+      <c r="L35" s="5">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="7:12">
+      <c r="G36" s="1">
+        <v>5400</v>
+      </c>
+      <c r="L36" s="5">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="12:15">
+      <c r="L37" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="3" t="s">
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="L33" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="9" t="s">
-        <v>80</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="9" t="s">
-        <v>81</v>
+      <c r="L38" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="9" t="s">
-        <v>82</v>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="L37:O37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="L38:O38"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A45:J45"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A38" r:id="rId1" display="https://www.bilibili.com/read/cv34684600"/>
-    <hyperlink ref="A39" r:id="rId2" display="https://tieba.baidu.com/p/10710367839" tooltip="https://tieba.baidu.com/p/10710367839"/>
-    <hyperlink ref="A40" r:id="rId3" display="https://www.warship1.cn/forum.php?mod=viewthread&amp;tid=7352"/>
+    <hyperlink ref="A43" r:id="rId1" display="https://www.bilibili.com/read/cv34684600"/>
+    <hyperlink ref="A44" r:id="rId2" display="https://tieba.baidu.com/p/10710367839" tooltip="https://tieba.baidu.com/p/10710367839"/>
+    <hyperlink ref="A45" r:id="rId3" display="https://www.warship1.cn/forum.php?mod=viewthread&amp;tid=7352"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -6525,7 +6585,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:39">
+    <row r="31" spans="1:42">
       <c r="A31" s="2">
         <v>1916</v>
       </c>
@@ -6560,51 +6620,59 @@
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
       <c r="Y31" s="5"/>
-      <c r="Z31" s="5" t="s">
+      <c r="AE31" s="22"/>
+      <c r="AF31" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="AA31" s="22" t="s">
+      <c r="AG31" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="AB31" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="AC31" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="AD31" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="AE31" s="22"/>
-      <c r="AF31" s="22"/>
-      <c r="AG31" s="22"/>
-      <c r="AH31" s="22"/>
-      <c r="AI31" s="22"/>
+      <c r="AH31" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI31" s="22" t="s">
+        <v>158</v>
+      </c>
       <c r="AJ31" s="22"/>
       <c r="AK31" s="5"/>
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
-    </row>
-    <row r="32" spans="26:30">
-      <c r="Z32" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA32" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB32" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="AC32" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD32" s="5" t="s">
-        <v>167</v>
+      <c r="AP31" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:42">
+      <c r="A32" s="1">
+        <v>1916</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF32" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="AG32" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="AH32" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI32" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="AP32" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:37">
       <c r="A33" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -6612,7 +6680,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -6629,11 +6697,21 @@
       <c r="W33" s="14"/>
       <c r="X33" s="14"/>
       <c r="Y33" s="14"/>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
-      <c r="AC33" s="14"/>
-      <c r="AD33" s="14"/>
+      <c r="Z33" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA33" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB33" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC33" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD33" s="22" t="s">
+        <v>166</v>
+      </c>
       <c r="AE33" s="14"/>
       <c r="AF33" s="14"/>
       <c r="AG33" s="14"/>
@@ -6642,9 +6720,9 @@
       <c r="AJ33" s="14"/>
       <c r="AK33" s="14"/>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:30">
       <c r="A34" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -6652,10 +6730,10 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -6669,10 +6747,25 @@
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
+      <c r="Z34" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA34" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB34" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AC34" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AD34" s="5" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -6681,7 +6774,7 @@
       <c r="F35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -6709,7 +6802,7 @@
         <v>85</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -6741,7 +6834,7 @@
     </row>
     <row r="37" spans="1:37">
       <c r="A37" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -6752,7 +6845,7 @@
         <v>85</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -6784,7 +6877,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -6794,7 +6887,7 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -6802,7 +6895,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -6819,7 +6912,7 @@
     </row>
     <row r="40" spans="1:19">
       <c r="A40" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -6827,7 +6920,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="N40" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
@@ -6837,7 +6930,7 @@
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -6853,7 +6946,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -6863,7 +6956,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -6873,7 +6966,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -6883,7 +6976,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -6893,7 +6986,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -6903,7 +6996,7 @@
     </row>
     <row r="47" spans="1:38">
       <c r="A47" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -6911,7 +7004,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
@@ -6931,7 +7024,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -6981,7 +7074,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AA31:AD31" numberStoredAsText="1"/>
+    <ignoredError sqref="AA33:AD33" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7027,7 +7120,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7044,7 +7137,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7061,7 +7154,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7078,7 +7171,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7095,7 +7188,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7112,7 +7205,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7129,7 +7222,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7146,7 +7239,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7163,7 +7256,7 @@
         <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7180,7 +7273,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7214,7 +7307,7 @@
         <v>37</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7231,7 +7324,7 @@
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7248,7 +7341,7 @@
         <v>44</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7265,7 +7358,7 @@
         <v>46</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7282,7 +7375,7 @@
         <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7299,7 +7392,7 @@
         <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="5:5">
@@ -7464,7 +7557,7 @@
     </row>
     <row r="31" spans="5:5">
       <c r="E31" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
